--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE44"/>
+  <dimension ref="A1:AE47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -5734,6 +5734,414 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0132</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0132a</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/10731911261469521</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Can We Differentiate Between Self-Reported Skills and Traits? A Possible Refinement of the BESSI and Its Validity in Italian High School Students</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Recent research has emphasized the conceptual distinction between personality traits and social, emotional, and behavioral (SEB) skills. However, their self-report measures show substantial empirical overlap. This study introduces and evaluates the Behavioral, Emotional, and Social Skills Inventoryâ€”Dual Rating (BESSI-Dual Rating), a modified version of the original BESSI designed to reduce this overlap. A sample of 598 Italian high school students completed the BESSI-Dual Rating, a Big Five personality inventory, and measures of academic and socio-emotional outcomes. Confirmatory factor analyses supported the structural validity of the BESSI-Dual Rating. Compared to previous BESSI validation studies, BESSI-Dual Rating scores showed improved discriminant and incremental validity relative to the corresponding traits. Furthermore, students perceived skill- and tendency-based items as meaningfully distinctâ€”contrary to findings from prior research using alternative instruments. Parent-reported SEB skills provided additional support for the validity of the skill measures. These findings suggest that minor but targeted refinements in questionnaire design can enhance the empirical differentiation between skills and traits. Â© The Author(s) 2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Pellegrino, Gerardo and Meneghetti, Chiara and Carretti, Barbara and Feraco, Tommaso</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Pellegrino et al.</t>
+        </is>
+      </c>
+      <c r="K45">
+        <v>2026</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>skillassessment;selfreport;otherreport;incrementalvalidity;skilltraitdifferences</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>tommaso.feraco@unipd.it</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17605/OSF.IO/829XR</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>17.11</t>
+        </is>
+      </c>
+      <c r="V45">
+        <v>598</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>school_age</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>bessi45dualrating</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>bf</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>also includes other report</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0134</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0134a</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.lindif.2026.102988</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Social, emotional, and behavioral skills as resources for student engagement: A one-year longitudinal study in high school students</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Social, emotional, and behavioral (SEB) skills refer to capacities that support social relationships, emotion regulation, and engagement with new experiences. These skills are considered crucial for high school students' academic success and well-being. The present study examined the longitudinal associations between five SEB skill domains (self-management, social engagement, cooperation, innovation, and emotional resilience) and four dimensions of student engagement (affective, behavioral, cognitive, and agentic). A sample of 1555 Italian high school students completed self-report measures of SEB skills and engagement at the beginning (T1), middle (T2), and end (T3) of the academic year. Latent change score modelling showed that student engagement generally declined across the school year, particularly between T1 and T2. However, students with higher levels of self-management, innovation, and social engagement at T1 showed smaller declines in engagement. Overall, these findings suggest that SEB skills help students sustain engagement, especially during the first part of the school year. Educational relevance statement: Social, emotional, and behavioral (SEB) skills are increasingly recognized as key competencies that foster student engagement in learning and academic activities. Using a comprehensive SEB framework and a three-wave longitudinal design, our study examined whether SEB skills contribute to the maintenance of engagement across the school year. Results indicated that students who reported higher levels of self-management, innovation, and social engagement also experienced smaller decreases in engagement, although the effects varied across engagement dimensions. Overall, these findings highlight the educational value of integrating SEB skills instruction into school curricula. Strengthening these skills may help students sustain engagement throughout the academic year, with potential benefits for academic achievement and well-being. Â© 2026 The Authors</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Learning and Individual Differences</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Pellegrino, Gerardo and Feraco, Tommaso and Meneghetti, Chiara and Carretti, Barbara</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Pellegrino et al.</t>
+        </is>
+      </c>
+      <c r="K46">
+        <v>2026</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>academicachievement;learningfactors;positiveschooloutcomes</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>gerardo.pellegrino@unipd.it</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://osf.io/hrws7</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="V46">
+        <v>1330</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>school_age</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Only T1 sample retained for the meta-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0138a</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://psycnet.apa.org/doi/10.1037/pspp0000610</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Self-Efficacy Predicts Differential Neuroticism Change in a Smartphone-Based Intervention</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Self-guided, digital interventions can help people change their personality traits in desired directions, including becoming less neurotic. However, little is known about how and why people differ in intervention-related changes. Theoretical models state that intentional personality change must be perceived as feasible and that being motivated to change is not sufficient to elicit lasting trait changes. Using a German-speaking sample (N = 446</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PERSONALITY AND SOCIAL PSYCHOLOGY</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Kramer, Michael D. and Wright, Amanda J. and Haehner, Peter and Zimmermann, Johannes and Fluckiger, Christoph and Hopwood, Christopher J. and Bleidorn, Wiebke</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Kramer et al.</t>
+        </is>
+      </c>
+      <c r="K47">
+        <v>2026</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>interventions;skilldevelopment</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>m.kraemer@psychologie.uzh.ch</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://www.swissubase.ch/en/catalogue/studies/21062/20966/overview</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="V47">
+        <v>446</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>bessi20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>bf</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE47"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -6142,6 +6142,147 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0141</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0141a</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/09388982261483237</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Understanding Academic Adjustment in Undergraduates With SLD or ADHD: An Integrative Model of Social-Emotional-Behavioral Skills, Academic Self-Efficacy, and Self-Regulated Learning</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Students with specific learning disorders (SLD) and/or attention-deficit/hyperactivity disorder (ADHD) often face challenges in higher education</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>LEARNING DISABILITIES RESEARCH \&amp; PRACTICE</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sharabi, Adi</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sharabi</t>
+        </is>
+      </c>
+      <c r="K48">
+        <v>2026</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>academicachievement; schoolsatisfaction; learningdisabilities; learningfactors</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>adi.sharabi@smkb.ac.il</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>25.49</t>
+        </is>
+      </c>
+      <c r="V48">
+        <v>525</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>young_adult</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>specific learning disabilities; adhd</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>bessi20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Participants included in previous study (0080a) were excluded from the meta-analysis sample.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
